--- a/dist/tally_templates/TNJP.xlsx
+++ b/dist/tally_templates/TNJP.xlsx
@@ -1522,7 +1522,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;-* #,##0_-;_-* -_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * -_ ;_ @_ "/>
@@ -2469,7 +2469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="413">
+  <cellXfs count="427">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3707,6 +3707,48 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3714,11 +3756,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3924,7 +3966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I81"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.9921875" customHeight="1"/>
   <cols>
@@ -3999,7 +4041,7 @@
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="413"/>
       <c r="C6" s="10"/>
       <c r="D6" s="9" t="s">
         <v>5</v>
@@ -4030,12 +4072,12 @@
       <c r="D8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="6"/>
+      <c r="E8" s="414"/>
       <c r="F8" s="1"/>
       <c r="G8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="1"/>
+      <c r="H8" s="413"/>
       <c r="I8" s="14"/>
     </row>
     <row r="9" ht="9.95" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4052,12 +4094,12 @@
       <c r="D10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="414"/>
       <c r="F10" s="1"/>
       <c r="G10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="1"/>
+      <c r="H10" s="413"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" ht="5.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4951,7 +4993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IW27"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.9921875" customHeight="1"/>
   <cols>
@@ -5267,7 +5309,7 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="415" t="s">
         <v>40</v>
       </c>
       <c r="C6" s="1"/>
@@ -5277,7 +5319,7 @@
       <c r="G6" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="122"/>
+      <c r="H6" s="416"/>
       <c r="I6" s="122"/>
       <c r="J6" s="1"/>
       <c r="K6" s="6" t="s">
@@ -5302,7 +5344,7 @@
       <c r="A8" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="415" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="111"/>
@@ -5312,7 +5354,7 @@
       <c r="G8" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="122" t="s">
+      <c r="H8" s="416" t="s">
         <v>44</v>
       </c>
       <c r="I8" s="122"/>
@@ -5320,7 +5362,7 @@
       <c r="K8" s="128" t="s">
         <v>45</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="126">
         <v>15</v>
       </c>
     </row>
@@ -5698,7 +5740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IW31"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.9921875" customHeight="1"/>
   <cols>
@@ -6025,7 +6067,7 @@
       <c r="A6" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="415" t="s">
         <v>40</v>
       </c>
       <c r="C6" s="1"/>
@@ -6037,7 +6079,7 @@
       <c r="I6" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="J6" s="1"/>
+      <c r="J6" s="413"/>
       <c r="K6" s="127"/>
       <c r="L6" s="127"/>
       <c r="M6" s="1"/>
@@ -6055,7 +6097,7 @@
       <c r="A8" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="127" t="s">
+      <c r="B8" s="416" t="s">
         <v>65</v>
       </c>
       <c r="C8" s="127"/>
@@ -6081,7 +6123,7 @@
       </c>
     </row>
     <row r="9" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" ht="12" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="129" t="s">
         <v>67</v>
       </c>
@@ -6115,7 +6157,7 @@
       <c r="Q10" s="129"/>
       <c r="R10" s="129"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="129"/>
       <c r="B11" s="129"/>
       <c r="C11" s="129"/>
@@ -6577,7 +6619,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IW28"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.9921875" customHeight="1"/>
   <cols>
@@ -6893,7 +6935,7 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="127" t="s">
+      <c r="B6" s="416" t="s">
         <v>40</v>
       </c>
       <c r="C6" s="1"/>
@@ -6903,7 +6945,7 @@
       <c r="G6" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="414"/>
       <c r="I6" s="4"/>
       <c r="J6" s="1"/>
       <c r="K6" s="6" t="str">
@@ -6929,7 +6971,7 @@
       <c r="A8" s="127" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="415" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="111"/>
@@ -6939,7 +6981,7 @@
       <c r="G8" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="122" t="s">
+      <c r="H8" s="416" t="s">
         <v>44</v>
       </c>
       <c r="I8" s="122"/>
@@ -7341,7 +7383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IW32"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.9921875" customHeight="1"/>
   <cols>
@@ -7667,7 +7709,7 @@
       <c r="A6" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="127" t="s">
+      <c r="B6" s="416" t="s">
         <v>40</v>
       </c>
       <c r="C6" s="1"/>
@@ -7679,7 +7721,7 @@
       <c r="I6" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J6" s="1"/>
+      <c r="J6" s="413"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="1"/>
@@ -7697,7 +7739,7 @@
       <c r="A8" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="127" t="s">
+      <c r="B8" s="416" t="s">
         <v>65</v>
       </c>
       <c r="C8" s="127"/>
@@ -7723,7 +7765,7 @@
       </c>
     </row>
     <row r="9" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" ht="12" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="129" t="s">
         <v>67</v>
       </c>
@@ -7757,7 +7799,7 @@
       <c r="Q10" s="129"/>
       <c r="R10" s="129"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="129"/>
       <c r="B11" s="129"/>
       <c r="C11" s="129"/>
@@ -8220,7 +8262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IW139"/>
   <sheetFormatPr defaultRowHeight="12" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.9921875" customHeight="1"/>
   <cols>
@@ -8537,7 +8579,7 @@
       <c r="A6" s="183" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="184" t="s">
+      <c r="B6" s="417" t="s">
         <v>40</v>
       </c>
       <c r="C6" s="183"/>
@@ -8547,7 +8589,7 @@
         <v>80</v>
       </c>
       <c r="G6" s="184"/>
-      <c r="H6" s="185"/>
+      <c r="H6" s="417"/>
       <c r="I6" s="183"/>
       <c r="J6" s="186" t="str">
         <f>'DM-IN'!O6</f>
@@ -8576,7 +8618,7 @@
       <c r="A8" s="183" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="183"/>
+      <c r="B8" s="418"/>
       <c r="C8" s="183"/>
       <c r="D8" s="183"/>
       <c r="E8" s="183"/>
@@ -8584,12 +8626,12 @@
         <v>82</v>
       </c>
       <c r="G8" s="184"/>
-      <c r="H8" s="185"/>
+      <c r="H8" s="417"/>
       <c r="I8" s="183"/>
       <c r="J8" s="183" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="185" t="s">
+      <c r="K8" s="417" t="s">
         <v>84</v>
       </c>
       <c r="L8" s="185" t="s">
@@ -10127,7 +10169,7 @@
       </c>
       <c r="B29" s="196"/>
       <c r="C29" s="196"/>
-      <c r="D29" s="197"/>
+      <c r="D29" s="419"/>
       <c r="E29" s="197"/>
       <c r="F29" s="197"/>
       <c r="G29" s="197"/>
@@ -13688,7 +13730,7 @@
       <c r="A55" s="183" t="s">
         <v>79</v>
       </c>
-      <c r="B55" s="184" t="s">
+      <c r="B55" s="417" t="s">
         <v>40</v>
       </c>
       <c r="C55" s="183"/>
@@ -13698,7 +13740,7 @@
         <v>80</v>
       </c>
       <c r="G55" s="184"/>
-      <c r="H55" s="219"/>
+      <c r="H55" s="420"/>
       <c r="I55" s="183"/>
       <c r="J55" s="186" t="str">
         <f>'OS-OUT'!K6</f>
@@ -13727,7 +13769,7 @@
       <c r="A57" s="183" t="s">
         <v>81</v>
       </c>
-      <c r="B57" s="183"/>
+      <c r="B57" s="418"/>
       <c r="C57" s="183"/>
       <c r="D57" s="183"/>
       <c r="E57" s="183"/>
@@ -13735,12 +13777,12 @@
         <v>82</v>
       </c>
       <c r="G57" s="184"/>
-      <c r="H57" s="185"/>
+      <c r="H57" s="417"/>
       <c r="I57" s="183"/>
       <c r="J57" s="183" t="s">
         <v>83</v>
       </c>
-      <c r="K57" s="185" t="s">
+      <c r="K57" s="417" t="s">
         <v>84</v>
       </c>
       <c r="L57" s="185" t="s">
@@ -15278,7 +15320,7 @@
       </c>
       <c r="B78" s="196"/>
       <c r="C78" s="196"/>
-      <c r="D78" s="197"/>
+      <c r="D78" s="419"/>
       <c r="E78" s="197"/>
       <c r="F78" s="197"/>
       <c r="G78" s="197"/>
@@ -22778,7 +22820,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q75"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.9921875" customHeight="1"/>
   <cols>
@@ -22855,7 +22897,7 @@
       <c r="A6" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="413"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
@@ -22864,7 +22906,7 @@
       <c r="F6" s="225" t="s">
         <v>122</v>
       </c>
-      <c r="G6" s="226" t="s">
+      <c r="G6" s="421" t="s">
         <v>37</v>
       </c>
     </row>
@@ -23338,7 +23380,7 @@
       <c r="A43" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B43" s="1"/>
+      <c r="B43" s="413"/>
       <c r="C43" s="269"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1" t="s">
@@ -23347,7 +23389,7 @@
       <c r="F43" s="225" t="s">
         <v>122</v>
       </c>
-      <c r="G43" s="226" t="s">
+      <c r="G43" s="421" t="s">
         <v>37</v>
       </c>
     </row>
@@ -23842,7 +23884,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IW135"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.9921875" customHeight="1"/>
   <cols>
@@ -24427,7 +24469,7 @@
       <c r="D6" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="413"/>
       <c r="F6" s="312"/>
       <c r="G6" s="6" t="str">
         <f>'OS-IN'!K6</f>
@@ -24453,7 +24495,7 @@
       <c r="G7" s="313" t="s">
         <v>122</v>
       </c>
-      <c r="H7" s="314" t="s">
+      <c r="H7" s="422" t="s">
         <v>137</v>
       </c>
       <c r="I7" s="314"/>
@@ -31688,7 +31730,7 @@
       <c r="D51" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E51" s="1"/>
+      <c r="E51" s="413"/>
       <c r="F51" s="312"/>
       <c r="G51" s="6" t="str">
         <f>G6</f>
@@ -31714,7 +31756,7 @@
       <c r="G52" s="313" t="s">
         <v>122</v>
       </c>
-      <c r="H52" s="314" t="s">
+      <c r="H52" s="422" t="s">
         <v>137</v>
       </c>
       <c r="I52" s="314"/>
@@ -38947,7 +38989,7 @@
       <c r="D96" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E96" s="269"/>
+      <c r="E96" s="423"/>
       <c r="F96" s="312"/>
       <c r="G96" s="6" t="str">
         <f>'OS-OUT'!K6</f>
@@ -38973,7 +39015,7 @@
       <c r="G97" s="313" t="s">
         <v>122</v>
       </c>
-      <c r="H97" s="314" t="s">
+      <c r="H97" s="422" t="s">
         <v>137</v>
       </c>
       <c r="I97" s="314"/>
@@ -45768,7 +45810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IW53"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="7.8671875" customHeight="1"/>
   <cols>
@@ -46077,20 +46119,20 @@
         <v>159</v>
       </c>
       <c r="B4" s="347"/>
-      <c r="C4" s="347"/>
+      <c r="C4" s="424"/>
       <c r="D4" s="347"/>
       <c r="E4" s="347"/>
       <c r="F4" s="347"/>
       <c r="G4" s="347" t="s">
         <v>160</v>
       </c>
-      <c r="H4" s="347"/>
+      <c r="H4" s="424"/>
       <c r="I4" s="347"/>
       <c r="J4" s="347"/>
       <c r="K4" s="348" t="s">
         <v>161</v>
       </c>
-      <c r="L4" s="349" t="s">
+      <c r="L4" s="424" t="s">
         <v>44</v>
       </c>
     </row>
@@ -46100,7 +46142,7 @@
       </c>
       <c r="B5" s="350"/>
       <c r="C5" s="350"/>
-      <c r="D5" s="351"/>
+      <c r="D5" s="425"/>
       <c r="E5" s="351"/>
       <c r="F5" s="351"/>
       <c r="G5" s="350" t="s">
@@ -46108,7 +46150,7 @@
       </c>
       <c r="H5" s="350"/>
       <c r="I5" s="350"/>
-      <c r="J5" s="351"/>
+      <c r="J5" s="425"/>
       <c r="K5" s="351"/>
       <c r="L5" s="351"/>
     </row>
@@ -46118,7 +46160,7 @@
       </c>
       <c r="B6" s="352"/>
       <c r="C6" s="352"/>
-      <c r="D6" s="351"/>
+      <c r="D6" s="425"/>
       <c r="E6" s="351"/>
       <c r="F6" s="351"/>
       <c r="G6" s="350" t="s">
@@ -46126,7 +46168,7 @@
       </c>
       <c r="H6" s="350"/>
       <c r="I6" s="350"/>
-      <c r="J6" s="351"/>
+      <c r="J6" s="425"/>
       <c r="K6" s="351"/>
       <c r="L6" s="351"/>
     </row>
@@ -46136,7 +46178,7 @@
       </c>
       <c r="B7" s="350"/>
       <c r="C7" s="350"/>
-      <c r="D7" s="351"/>
+      <c r="D7" s="425"/>
       <c r="E7" s="351"/>
       <c r="F7" s="351"/>
       <c r="G7" s="342" t="s">
@@ -46144,7 +46186,7 @@
       </c>
       <c r="H7" s="342"/>
       <c r="I7" s="342"/>
-      <c r="J7" s="351"/>
+      <c r="J7" s="425"/>
       <c r="K7" s="351"/>
       <c r="L7" s="351"/>
     </row>
@@ -46423,7 +46465,7 @@
         <v>183</v>
       </c>
       <c r="G23" s="387"/>
-      <c r="H23" s="387" t="s">
+      <c r="H23" s="426" t="s">
         <v>184</v>
       </c>
       <c r="I23" s="387"/>
